--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit5_2_DownSamplingR.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit5_2_DownSamplingR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4107F5-A4AE-4760-9EE7-6B29B63C980B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D726844D-D339-4BF9-95CF-C6DF199BBDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{427F1CDB-5AAB-483C-A031-4C1182026265}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>記得存後半</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>input tile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -458,6 +454,10 @@
   </si>
   <si>
     <t>002306_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -705,10 +705,37 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -720,34 +747,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1134,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>9</v>
@@ -1211,42 +1211,42 @@
         <v>23</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="N5" t="s">
-        <v>24</v>
+        <v>94</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="D7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
       <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="O7" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -1258,62 +1258,62 @@
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
       <c r="L8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="11">
         <v>0</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
       <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
@@ -1326,23 +1326,23 @@
       <c r="V9" s="10"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C10" s="17"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
       <c r="L10" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M10" s="14"/>
       <c r="N10" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P10" s="14"/>
       <c r="Q10" s="5">
@@ -1350,32 +1350,32 @@
         <v>0</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
       <c r="U10" s="10"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C11" s="17"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
       <c r="L11" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
@@ -1384,38 +1384,38 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="E12" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
       <c r="L12" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
@@ -1427,62 +1427,62 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
       <c r="L13" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P13" s="11">
         <v>0</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
       <c r="L14" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
@@ -1490,36 +1490,36 @@
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V14" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
       <c r="L15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="14"/>
       <c r="N15" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P15" s="14"/>
       <c r="Q15" s="5">
@@ -1527,31 +1527,31 @@
         <v>192</v>
       </c>
       <c r="R15" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S15" s="10"/>
       <c r="U15" s="10"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
       <c r="L16" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
@@ -1560,40 +1560,40 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
+      <c r="F17" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
       <c r="L17" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -1605,62 +1605,62 @@
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P18" s="11">
         <v>0</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R18" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C19" s="17"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
@@ -1668,36 +1668,36 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V19" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C20" s="17"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M20" s="14"/>
       <c r="N20" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P20" s="14"/>
       <c r="Q20" s="5">
@@ -1705,32 +1705,32 @@
         <v>384</v>
       </c>
       <c r="R20" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C21" s="17"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
       <c r="Q21" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
@@ -1738,38 +1738,38 @@
       <c r="U21" s="10"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C22" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="23"/>
-      <c r="F22" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="17"/>
+      <c r="C22" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="21"/>
       <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
@@ -1778,62 +1778,62 @@
       <c r="U22" s="10"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="21"/>
       <c r="L23" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P23" s="11">
         <v>1</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="17"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="21"/>
       <c r="L24" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
@@ -1841,62 +1841,62 @@
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V24" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="17"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="21"/>
       <c r="L25" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M25" s="14"/>
       <c r="N25" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P25" s="14"/>
       <c r="Q25" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R25" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="21"/>
       <c r="L26" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
@@ -1915,45 +1915,45 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="17"/>
+      <c r="J29" s="21"/>
       <c r="L29" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N29" s="9">
         <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -1965,62 +1965,62 @@
       <c r="B30">
         <v>3</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="17"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="21"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P30" s="11">
         <v>0</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="21"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
@@ -2028,36 +2028,36 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V31" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="21"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M32" s="14"/>
       <c r="N32" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P32" s="14"/>
       <c r="Q32" s="5">
@@ -2065,32 +2065,32 @@
         <v>576</v>
       </c>
       <c r="R32" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="17"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="21"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
       <c r="Q33" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
@@ -2098,40 +2098,40 @@
       <c r="U33" s="10"/>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C34" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>27</v>
+      <c r="C34" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L34" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P34" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
@@ -2140,62 +2140,62 @@
       <c r="U34" s="10"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="22"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="26"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P35" s="11">
         <v>0</v>
       </c>
       <c r="Q35" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R35" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R35" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S35" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="22"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="26"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N36" s="10"/>
       <c r="O36" s="10"/>
@@ -2203,62 +2203,62 @@
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V36" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="22"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="26"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M37" s="14"/>
       <c r="N37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O37" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P37" s="14"/>
       <c r="Q37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R37" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="22"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="26"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
@@ -2271,44 +2271,44 @@
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="17"/>
-      <c r="J39" s="27" t="s">
-        <v>34</v>
+      <c r="F39" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="21"/>
+      <c r="J39" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L39" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -2320,65 +2320,65 @@
       <c r="B40">
         <v>4</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="27"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="20"/>
       <c r="L40" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P40" s="11">
         <v>0</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V40" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B41" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="20"/>
       <c r="L41" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
@@ -2386,30 +2386,30 @@
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
       <c r="S41" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V41" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>0</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="27"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="20"/>
       <c r="L42" s="14" t="s">
         <v>17</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="5">
@@ -2427,34 +2427,34 @@
         <v>768</v>
       </c>
       <c r="R42" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
       <c r="U42" s="10"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C43" s="17"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="27"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="20"/>
       <c r="L43" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
       <c r="Q43" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
@@ -2462,40 +2462,40 @@
       <c r="U43" s="10"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C44" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="23"/>
-      <c r="F44" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J44" s="17"/>
+      <c r="C44" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="22"/>
+      <c r="F44" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" s="21"/>
       <c r="L44" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P44" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
@@ -2504,62 +2504,62 @@
       <c r="U44" s="10"/>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="17"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="21"/>
       <c r="L45" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P45" s="11">
         <v>1</v>
       </c>
       <c r="Q45" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R45" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S45" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S45" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T45" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V45" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="17"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="21"/>
       <c r="L46" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
@@ -2567,62 +2567,62 @@
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
       <c r="S46" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T46" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V46" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="17"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="21"/>
       <c r="L47" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M47" s="14"/>
       <c r="N47" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P47" s="14"/>
       <c r="Q47" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R47" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S47" s="10"/>
       <c r="T47" s="10"/>
       <c r="U47" s="10"/>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="17"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="21"/>
       <c r="L48" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N48" s="10"/>
       <c r="O48" s="10"/>
@@ -2638,42 +2638,42 @@
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J50" s="17"/>
+      <c r="E50" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="21"/>
+      <c r="I50" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="21"/>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q50" s="10"/>
       <c r="R50" s="10"/>
@@ -2685,62 +2685,62 @@
       <c r="B51">
         <v>5</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="17"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="21"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P51" s="11">
         <v>0</v>
       </c>
       <c r="Q51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R51" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T51" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V51" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C52" s="17"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="17"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="21"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M52" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N52" s="10"/>
       <c r="O52" s="10"/>
@@ -2748,36 +2748,36 @@
       <c r="Q52" s="10"/>
       <c r="R52" s="10"/>
       <c r="S52" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T52" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V52" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="17"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="21"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M53" s="14"/>
       <c r="N53" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="5">
@@ -2785,32 +2785,32 @@
         <v>960</v>
       </c>
       <c r="R53" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="10"/>
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C54" s="17"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="17"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="21"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
       <c r="P54" s="10"/>
       <c r="Q54" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R54" s="10"/>
       <c r="S54" s="10"/>
@@ -2818,40 +2818,40 @@
       <c r="U54" s="10"/>
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C55" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J55" s="22" t="s">
-        <v>27</v>
+      <c r="C55" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="21"/>
+      <c r="I55" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L55" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -2860,62 +2860,62 @@
       <c r="U55" s="10"/>
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="22"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="26"/>
       <c r="L56" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P56" s="11">
         <v>0</v>
       </c>
       <c r="Q56" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R56" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R56" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S56" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V56" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="22"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="26"/>
       <c r="L57" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
@@ -2923,62 +2923,62 @@
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
       <c r="S57" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T57" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V57" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="22"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="26"/>
       <c r="L58" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M58" s="14"/>
       <c r="N58" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P58" s="14"/>
       <c r="Q58" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R58" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S58" s="10"/>
       <c r="T58" s="10"/>
       <c r="U58" s="10"/>
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="22"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="26"/>
       <c r="L59" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N59" s="10"/>
       <c r="O59" s="10"/>
@@ -2991,44 +2991,44 @@
     </row>
     <row r="60" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B60" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D60" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="27" t="s">
-        <v>34</v>
+      <c r="F60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="21"/>
+      <c r="J60" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N60" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P60" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q60" s="10"/>
       <c r="R60" s="10"/>
@@ -3040,65 +3040,65 @@
       <c r="B61">
         <v>6</v>
       </c>
-      <c r="C61" s="17"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="27"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="20"/>
       <c r="L61" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N61" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O61" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P61" s="11">
         <v>0</v>
       </c>
       <c r="Q61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R61" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V61" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B62" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C62" s="17"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C62" s="21"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="20"/>
       <c r="L62" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N62" s="10"/>
       <c r="O62" s="10"/>
@@ -3106,30 +3106,30 @@
       <c r="Q62" s="10"/>
       <c r="R62" s="10"/>
       <c r="S62" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T62" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U62" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V62" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B63">
         <v>1</v>
       </c>
-      <c r="C63" s="17"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="27"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="20"/>
       <c r="L63" s="14" t="s">
         <v>17</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>192</v>
       </c>
       <c r="O63" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P63" s="14"/>
       <c r="Q63" s="5">
@@ -3147,34 +3147,34 @@
         <v>1152</v>
       </c>
       <c r="R63" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S63" s="10"/>
       <c r="T63" s="10"/>
       <c r="U63" s="10"/>
     </row>
     <row r="64" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C64" s="17"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="27"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="20"/>
       <c r="L64" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M64" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
       <c r="Q64" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R64" s="10"/>
       <c r="S64" s="10"/>
@@ -3182,40 +3182,40 @@
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C65" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E65" s="23"/>
-      <c r="F65" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I65" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J65" s="17"/>
+      <c r="C65" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I65" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="21"/>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -3224,62 +3224,62 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="17"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="21"/>
       <c r="L66" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M66" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P66" s="11">
         <v>1</v>
       </c>
       <c r="Q66" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R66" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S66" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S66" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T66" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V66" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="17"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="21"/>
       <c r="L67" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M67" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N67" s="10"/>
       <c r="O67" s="10"/>
@@ -3287,62 +3287,62 @@
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
       <c r="S67" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T67" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V67" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="17"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="21"/>
       <c r="L68" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M68" s="14"/>
       <c r="N68" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R68" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S68" s="10"/>
       <c r="T68" s="10"/>
       <c r="U68" s="10"/>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="17"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="21"/>
       <c r="L69" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M69" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N69" s="10"/>
       <c r="O69" s="10"/>
@@ -3358,42 +3358,42 @@
     </row>
     <row r="71" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B71" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D71" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I71" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J71" s="17"/>
+      <c r="E71" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F71" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J71" s="21"/>
       <c r="L71" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -3405,62 +3405,62 @@
       <c r="B72">
         <v>7</v>
       </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="17"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="24"/>
+      <c r="J72" s="21"/>
       <c r="L72" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P72" s="11">
         <v>0</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V72" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C73" s="17"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="17"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="21"/>
       <c r="L73" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M73" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N73" s="10"/>
       <c r="O73" s="10"/>
@@ -3468,36 +3468,36 @@
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
       <c r="S73" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T73" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U73" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V73" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C74" s="17"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="17"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="21"/>
       <c r="L74" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M74" s="14"/>
       <c r="N74" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P74" s="14"/>
       <c r="Q74" s="5">
@@ -3505,32 +3505,32 @@
         <v>1344</v>
       </c>
       <c r="R74" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S74" s="10"/>
       <c r="T74" s="10"/>
       <c r="U74" s="10"/>
     </row>
     <row r="75" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="17"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="21"/>
       <c r="L75" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M75" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N75" s="10"/>
       <c r="O75" s="10"/>
       <c r="P75" s="10"/>
       <c r="Q75" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
@@ -3538,40 +3538,40 @@
       <c r="U75" s="10"/>
     </row>
     <row r="76" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C76" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I76" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J76" s="22" t="s">
-        <v>27</v>
+      <c r="C76" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J76" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L76" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N76" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P76" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q76" s="10"/>
       <c r="R76" s="10"/>
@@ -3580,62 +3580,62 @@
       <c r="U76" s="10"/>
     </row>
     <row r="77" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="22"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="26"/>
       <c r="L77" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M77" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N77" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O77" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P77" s="11">
         <v>0</v>
       </c>
       <c r="Q77" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R77" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R77" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S77" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T77" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V77" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="18"/>
-      <c r="J78" s="22"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="26"/>
       <c r="L78" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M78" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N78" s="10"/>
       <c r="O78" s="10"/>
@@ -3643,62 +3643,62 @@
       <c r="Q78" s="10"/>
       <c r="R78" s="10"/>
       <c r="S78" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T78" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V78" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="22"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="26"/>
       <c r="L79" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M79" s="14"/>
       <c r="N79" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P79" s="14"/>
       <c r="Q79" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R79" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="10"/>
     </row>
     <row r="80" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="22"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="26"/>
       <c r="L80" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M80" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N80" s="10"/>
       <c r="O80" s="10"/>
@@ -3711,44 +3711,44 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D81" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I81" s="17"/>
-      <c r="J81" s="27" t="s">
-        <v>34</v>
+      <c r="F81" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" s="21"/>
+      <c r="J81" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -3760,65 +3760,65 @@
       <c r="B82">
         <v>8</v>
       </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="27"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="20"/>
       <c r="L82" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N82" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O82" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P82" s="11">
         <v>0</v>
       </c>
       <c r="Q82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R82" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T82" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V82" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B83" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C83" s="21"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="20"/>
       <c r="L83" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M83" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N83" s="10"/>
       <c r="O83" s="10"/>
@@ -3826,30 +3826,30 @@
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
       <c r="S83" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T83" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V83" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B84">
         <v>2</v>
       </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="27"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="20"/>
       <c r="L84" s="14" t="s">
         <v>17</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>384</v>
       </c>
       <c r="O84" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="5">
@@ -3867,34 +3867,34 @@
         <v>1536</v>
       </c>
       <c r="R84" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S84" s="10"/>
       <c r="T84" s="10"/>
       <c r="U84" s="10"/>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C85" s="17"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="27"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="20"/>
       <c r="L85" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M85" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O85" s="10"/>
       <c r="P85" s="10"/>
       <c r="Q85" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R85" s="10"/>
       <c r="S85" s="10"/>
@@ -3902,40 +3902,40 @@
       <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C86" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D86" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E86" s="23"/>
-      <c r="F86" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G86" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H86" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I86" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J86" s="23"/>
+      <c r="C86" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="22"/>
+      <c r="F86" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H86" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I86" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" s="22"/>
       <c r="L86" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N86" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P86" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q86" s="10"/>
       <c r="R86" s="10"/>
@@ -3944,62 +3944,62 @@
       <c r="U86" s="10"/>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="23"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="22"/>
       <c r="L87" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N87" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P87" s="11">
         <v>1</v>
       </c>
       <c r="Q87" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R87" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S87" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S87" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T87" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V87" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="22"/>
-      <c r="J88" s="23"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="22"/>
       <c r="L88" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M88" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N88" s="10"/>
       <c r="O88" s="10"/>
@@ -4007,62 +4007,62 @@
       <c r="Q88" s="10"/>
       <c r="R88" s="10"/>
       <c r="S88" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T88" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V88" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="22"/>
-      <c r="J89" s="23"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="22"/>
       <c r="L89" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M89" s="14"/>
       <c r="N89" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O89" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P89" s="14"/>
       <c r="Q89" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R89" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S89" s="10"/>
       <c r="T89" s="10"/>
       <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="18"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="23"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="22"/>
       <c r="L90" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M90" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N90" s="10"/>
       <c r="O90" s="10"/>
@@ -4081,45 +4081,45 @@
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C93" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D93" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D93" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E93" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F93" s="23"/>
-      <c r="G93" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H93" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I93" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J93" s="17"/>
+      <c r="E93" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="22"/>
+      <c r="G93" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H93" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I93" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J93" s="21"/>
       <c r="L93" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N93" s="9">
         <v>101</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -4131,62 +4131,62 @@
       <c r="B94">
         <v>9</v>
       </c>
-      <c r="C94" s="17"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="26"/>
-      <c r="J94" s="17"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="21"/>
       <c r="L94" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M94" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N94" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O94" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P94" s="11">
         <v>0</v>
       </c>
       <c r="Q94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T94" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V94" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C95" s="17"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="22"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="17"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="21"/>
       <c r="L95" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M95" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N95" s="10"/>
       <c r="O95" s="10"/>
@@ -4194,36 +4194,36 @@
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
       <c r="S95" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T95" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U95" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V95" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="C96" s="17"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="22"/>
-      <c r="I96" s="26"/>
-      <c r="J96" s="17"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="21"/>
       <c r="L96" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M96" s="14"/>
       <c r="N96" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O96" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P96" s="14"/>
       <c r="Q96" s="5">
@@ -4231,32 +4231,32 @@
         <v>1728</v>
       </c>
       <c r="R96" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S96" s="10"/>
       <c r="T96" s="10"/>
       <c r="U96" s="10"/>
     </row>
     <row r="97" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C97" s="17"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="17"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="21"/>
       <c r="L97" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M97" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N97" s="10"/>
       <c r="O97" s="10"/>
       <c r="P97" s="10"/>
       <c r="Q97" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R97" s="10"/>
       <c r="S97" s="10"/>
@@ -4264,40 +4264,40 @@
       <c r="U97" s="10"/>
     </row>
     <row r="98" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C98" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D98" s="17"/>
-      <c r="E98" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F98" s="23"/>
-      <c r="G98" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H98" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I98" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J98" s="22" t="s">
-        <v>27</v>
+      <c r="C98" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="22"/>
+      <c r="G98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J98" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L98" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M98" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N98" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P98" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q98" s="10"/>
       <c r="R98" s="10"/>
@@ -4306,62 +4306,62 @@
       <c r="U98" s="10"/>
     </row>
     <row r="99" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="18"/>
-      <c r="J99" s="22"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="26"/>
       <c r="L99" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M99" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N99" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O99" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P99" s="11">
         <v>0</v>
       </c>
       <c r="Q99" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R99" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R99" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S99" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T99" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V99" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="23"/>
-      <c r="G100" s="17"/>
-      <c r="H100" s="17"/>
-      <c r="I100" s="18"/>
-      <c r="J100" s="22"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="21"/>
+      <c r="H100" s="21"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="26"/>
       <c r="L100" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M100" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N100" s="10"/>
       <c r="O100" s="10"/>
@@ -4369,62 +4369,62 @@
       <c r="Q100" s="10"/>
       <c r="R100" s="10"/>
       <c r="S100" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T100" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U100" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V100" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C101" s="17"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="17"/>
-      <c r="H101" s="17"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="22"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="21"/>
+      <c r="H101" s="21"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="26"/>
       <c r="L101" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M101" s="14"/>
       <c r="N101" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P101" s="14"/>
       <c r="Q101" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R101" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S101" s="10"/>
       <c r="T101" s="10"/>
       <c r="U101" s="10"/>
     </row>
     <row r="102" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="22"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="21"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="26"/>
       <c r="L102" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M102" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N102" s="10"/>
       <c r="O102" s="10"/>
@@ -4437,44 +4437,44 @@
     </row>
     <row r="103" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C103" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D103" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F103" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G103" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I103" s="17"/>
-      <c r="J103" s="27" t="s">
-        <v>34</v>
+      <c r="F103" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H103" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I103" s="21"/>
+      <c r="J103" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L103" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -4486,65 +4486,65 @@
       <c r="B104">
         <v>10</v>
       </c>
-      <c r="C104" s="17"/>
-      <c r="D104" s="23"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="22"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="17"/>
-      <c r="I104" s="17"/>
-      <c r="J104" s="27"/>
+      <c r="C104" s="21"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="26"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="21"/>
+      <c r="J104" s="20"/>
       <c r="L104" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M104" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N104" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O104" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P104" s="11">
         <v>0</v>
       </c>
       <c r="Q104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T104" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V104" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B105" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C105" s="17"/>
-      <c r="D105" s="23"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="17"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="17"/>
-      <c r="J105" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C105" s="21"/>
+      <c r="D105" s="22"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="26"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="21"/>
+      <c r="J105" s="20"/>
       <c r="L105" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M105" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N105" s="10"/>
       <c r="O105" s="10"/>
@@ -4552,30 +4552,30 @@
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
       <c r="S105" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T105" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U105" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V105" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B106">
         <v>3</v>
       </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="18"/>
-      <c r="F106" s="22"/>
-      <c r="G106" s="17"/>
-      <c r="H106" s="17"/>
-      <c r="I106" s="17"/>
-      <c r="J106" s="27"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="21"/>
+      <c r="I106" s="21"/>
+      <c r="J106" s="20"/>
       <c r="L106" s="14" t="s">
         <v>17</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>576</v>
       </c>
       <c r="O106" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P106" s="14"/>
       <c r="Q106" s="5">
@@ -4593,34 +4593,34 @@
         <v>1920</v>
       </c>
       <c r="R106" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S106" s="10"/>
       <c r="T106" s="10"/>
       <c r="U106" s="10"/>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C107" s="17"/>
-      <c r="D107" s="23"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="22"/>
-      <c r="G107" s="17"/>
-      <c r="H107" s="17"/>
-      <c r="I107" s="17"/>
-      <c r="J107" s="27"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="22"/>
+      <c r="E107" s="25"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="21"/>
+      <c r="J107" s="20"/>
       <c r="L107" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M107" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O107" s="10"/>
       <c r="P107" s="10"/>
       <c r="Q107" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R107" s="10"/>
       <c r="S107" s="10"/>
@@ -4628,40 +4628,40 @@
       <c r="U107" s="10"/>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C108" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D108" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G108" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H108" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I108" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J108" s="17"/>
+      <c r="C108" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="22"/>
+      <c r="F108" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H108" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I108" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" s="21"/>
       <c r="L108" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M108" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N108" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P108" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q108" s="10"/>
       <c r="R108" s="10"/>
@@ -4670,62 +4670,62 @@
       <c r="U108" s="10"/>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C109" s="17"/>
-      <c r="D109" s="17"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="18"/>
-      <c r="I109" s="22"/>
-      <c r="J109" s="17"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
+      <c r="H109" s="25"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="21"/>
       <c r="L109" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M109" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N109" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O109" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P109" s="11">
         <v>1</v>
       </c>
       <c r="Q109" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R109" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S109" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S109" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T109" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V109" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C110" s="17"/>
-      <c r="D110" s="17"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="18"/>
-      <c r="I110" s="22"/>
-      <c r="J110" s="17"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
+      <c r="I110" s="26"/>
+      <c r="J110" s="21"/>
       <c r="L110" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M110" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N110" s="10"/>
       <c r="O110" s="10"/>
@@ -4733,62 +4733,62 @@
       <c r="Q110" s="10"/>
       <c r="R110" s="10"/>
       <c r="S110" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T110" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U110" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V110" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C111" s="17"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="22"/>
-      <c r="J111" s="17"/>
+      <c r="C111" s="21"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
+      <c r="I111" s="26"/>
+      <c r="J111" s="21"/>
       <c r="L111" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M111" s="14"/>
       <c r="N111" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O111" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P111" s="14"/>
       <c r="Q111" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R111" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S111" s="10"/>
       <c r="T111" s="10"/>
       <c r="U111" s="10"/>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C112" s="17"/>
-      <c r="D112" s="17"/>
-      <c r="E112" s="23"/>
-      <c r="F112" s="18"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="22"/>
-      <c r="J112" s="17"/>
+      <c r="C112" s="21"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+      <c r="H112" s="25"/>
+      <c r="I112" s="26"/>
+      <c r="J112" s="21"/>
       <c r="L112" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M112" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N112" s="10"/>
       <c r="O112" s="10"/>
@@ -4804,42 +4804,42 @@
     </row>
     <row r="114" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C114" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D114" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E114" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F114" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G114" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H114" s="17"/>
-      <c r="I114" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J114" s="17"/>
+      <c r="E114" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H114" s="21"/>
+      <c r="I114" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J114" s="21"/>
       <c r="L114" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M114" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N114" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O114" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P114" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q114" s="10"/>
       <c r="R114" s="10"/>
@@ -4851,62 +4851,62 @@
       <c r="B115">
         <v>11</v>
       </c>
-      <c r="C115" s="17"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="23"/>
-      <c r="F115" s="17"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="17"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="17"/>
+      <c r="C115" s="21"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="21"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="21"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="21"/>
       <c r="L115" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M115" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N115" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O115" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P115" s="11">
         <v>0</v>
       </c>
       <c r="Q115" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R115" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S115" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T115" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V115" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C116" s="17"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="23"/>
-      <c r="F116" s="17"/>
-      <c r="G116" s="22"/>
-      <c r="H116" s="17"/>
-      <c r="I116" s="26"/>
-      <c r="J116" s="17"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="25"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="26"/>
+      <c r="H116" s="21"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="21"/>
       <c r="L116" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M116" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
@@ -4914,36 +4914,36 @@
       <c r="Q116" s="10"/>
       <c r="R116" s="10"/>
       <c r="S116" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T116" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U116" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V116" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C117" s="17"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="17"/>
-      <c r="G117" s="22"/>
-      <c r="H117" s="17"/>
-      <c r="I117" s="26"/>
-      <c r="J117" s="17"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="25"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="21"/>
+      <c r="G117" s="26"/>
+      <c r="H117" s="21"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="21"/>
       <c r="L117" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M117" s="14"/>
       <c r="N117" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O117" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P117" s="14"/>
       <c r="Q117" s="5">
@@ -4951,32 +4951,32 @@
         <v>2112</v>
       </c>
       <c r="R117" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S117" s="10"/>
       <c r="T117" s="10"/>
       <c r="U117" s="10"/>
     </row>
     <row r="118" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C118" s="17"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="23"/>
-      <c r="F118" s="17"/>
-      <c r="G118" s="22"/>
-      <c r="H118" s="17"/>
-      <c r="I118" s="26"/>
-      <c r="J118" s="17"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="25"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="26"/>
+      <c r="H118" s="21"/>
+      <c r="I118" s="24"/>
+      <c r="J118" s="21"/>
       <c r="L118" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M118" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N118" s="10"/>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
       <c r="Q118" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R118" s="10"/>
       <c r="S118" s="10"/>
@@ -4984,40 +4984,40 @@
       <c r="U118" s="10"/>
     </row>
     <row r="119" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C119" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G119" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H119" s="17"/>
-      <c r="I119" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J119" s="22" t="s">
-        <v>27</v>
+      <c r="C119" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D119" s="21"/>
+      <c r="E119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H119" s="21"/>
+      <c r="I119" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J119" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L119" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M119" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -5026,62 +5026,62 @@
       <c r="U119" s="10"/>
     </row>
     <row r="120" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="17"/>
-      <c r="F120" s="17"/>
-      <c r="G120" s="17"/>
-      <c r="H120" s="17"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="22"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="21"/>
+      <c r="I120" s="25"/>
+      <c r="J120" s="26"/>
       <c r="L120" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M120" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N120" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O120" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P120" s="11">
         <v>0</v>
       </c>
       <c r="Q120" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R120" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R120" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S120" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T120" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V120" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-      <c r="G121" s="17"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="22"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="21"/>
+      <c r="I121" s="25"/>
+      <c r="J121" s="26"/>
       <c r="L121" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M121" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N121" s="10"/>
       <c r="O121" s="10"/>
@@ -5089,62 +5089,62 @@
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
       <c r="S121" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T121" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U121" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V121" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C122" s="17"/>
-      <c r="D122" s="17"/>
-      <c r="E122" s="17"/>
-      <c r="F122" s="17"/>
-      <c r="G122" s="17"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="22"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="21"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="26"/>
       <c r="L122" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M122" s="14"/>
       <c r="N122" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O122" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P122" s="14"/>
       <c r="Q122" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R122" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S122" s="10"/>
       <c r="T122" s="10"/>
       <c r="U122" s="10"/>
     </row>
     <row r="123" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C123" s="17"/>
-      <c r="D123" s="17"/>
-      <c r="E123" s="17"/>
-      <c r="F123" s="17"/>
-      <c r="G123" s="17"/>
-      <c r="H123" s="17"/>
-      <c r="I123" s="18"/>
-      <c r="J123" s="22"/>
+      <c r="C123" s="21"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21"/>
+      <c r="F123" s="21"/>
+      <c r="G123" s="21"/>
+      <c r="H123" s="21"/>
+      <c r="I123" s="25"/>
+      <c r="J123" s="26"/>
       <c r="L123" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M123" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N123" s="10"/>
       <c r="O123" s="10"/>
@@ -5157,44 +5157,44 @@
     </row>
     <row r="124" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E124" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E124" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F124" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G124" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H124" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I124" s="17"/>
-      <c r="J124" s="27" t="s">
-        <v>34</v>
+      <c r="F124" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I124" s="21"/>
+      <c r="J124" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L124" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M124" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N124" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O124" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P124" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q124" s="10"/>
       <c r="R124" s="10"/>
@@ -5206,65 +5206,65 @@
       <c r="B125">
         <v>12</v>
       </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="23"/>
-      <c r="E125" s="18"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
-      <c r="H125" s="22"/>
-      <c r="I125" s="17"/>
-      <c r="J125" s="27"/>
+      <c r="C125" s="21"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="21"/>
+      <c r="G125" s="21"/>
+      <c r="H125" s="26"/>
+      <c r="I125" s="21"/>
+      <c r="J125" s="20"/>
       <c r="L125" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M125" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N125" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O125" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P125" s="11">
         <v>0</v>
       </c>
       <c r="Q125" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R125" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S125" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T125" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V125" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B126" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C126" s="17"/>
-      <c r="D126" s="23"/>
-      <c r="E126" s="18"/>
-      <c r="F126" s="17"/>
-      <c r="G126" s="17"/>
-      <c r="H126" s="22"/>
-      <c r="I126" s="17"/>
-      <c r="J126" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C126" s="21"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="25"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="26"/>
+      <c r="I126" s="21"/>
+      <c r="J126" s="20"/>
       <c r="L126" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M126" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N126" s="10"/>
       <c r="O126" s="10"/>
@@ -5272,30 +5272,30 @@
       <c r="Q126" s="10"/>
       <c r="R126" s="10"/>
       <c r="S126" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T126" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U126" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V126" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B127">
         <v>4</v>
       </c>
-      <c r="C127" s="17"/>
-      <c r="D127" s="23"/>
-      <c r="E127" s="18"/>
-      <c r="F127" s="17"/>
-      <c r="G127" s="17"/>
-      <c r="H127" s="22"/>
-      <c r="I127" s="17"/>
-      <c r="J127" s="27"/>
+      <c r="C127" s="21"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="26"/>
+      <c r="I127" s="21"/>
+      <c r="J127" s="20"/>
       <c r="L127" s="14" t="s">
         <v>17</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>768</v>
       </c>
       <c r="O127" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P127" s="14"/>
       <c r="Q127" s="5">
@@ -5313,34 +5313,34 @@
         <v>2304</v>
       </c>
       <c r="R127" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S127" s="10"/>
       <c r="T127" s="10"/>
       <c r="U127" s="10"/>
     </row>
     <row r="128" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C128" s="17"/>
-      <c r="D128" s="23"/>
-      <c r="E128" s="18"/>
-      <c r="F128" s="17"/>
-      <c r="G128" s="17"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="17"/>
-      <c r="J128" s="27"/>
+      <c r="C128" s="21"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="21"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="21"/>
+      <c r="J128" s="20"/>
       <c r="L128" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M128" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N128" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O128" s="10"/>
       <c r="P128" s="10"/>
       <c r="Q128" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R128" s="10"/>
       <c r="S128" s="10"/>
@@ -5348,40 +5348,40 @@
       <c r="U128" s="10"/>
     </row>
     <row r="129" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C129" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E129" s="23"/>
-      <c r="F129" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G129" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H129" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I129" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J129" s="17"/>
+      <c r="C129" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D129" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E129" s="22"/>
+      <c r="F129" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G129" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H129" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I129" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" s="21"/>
       <c r="L129" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M129" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -5390,62 +5390,62 @@
       <c r="U129" s="10"/>
     </row>
     <row r="130" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C130" s="17"/>
-      <c r="D130" s="17"/>
-      <c r="E130" s="23"/>
-      <c r="F130" s="18"/>
-      <c r="G130" s="18"/>
-      <c r="H130" s="18"/>
-      <c r="I130" s="22"/>
-      <c r="J130" s="17"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="21"/>
       <c r="L130" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M130" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N130" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O130" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P130" s="11">
         <v>1</v>
       </c>
       <c r="Q130" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R130" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S130" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S130" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T130" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V130" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="131" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C131" s="17"/>
-      <c r="D131" s="17"/>
-      <c r="E131" s="23"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="22"/>
-      <c r="J131" s="17"/>
+      <c r="C131" s="21"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="25"/>
+      <c r="G131" s="25"/>
+      <c r="H131" s="25"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="21"/>
       <c r="L131" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M131" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N131" s="10"/>
       <c r="O131" s="10"/>
@@ -5453,62 +5453,62 @@
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
       <c r="S131" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T131" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U131" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V131" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C132" s="17"/>
-      <c r="D132" s="17"/>
-      <c r="E132" s="23"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="18"/>
-      <c r="H132" s="18"/>
-      <c r="I132" s="22"/>
-      <c r="J132" s="17"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="25"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="25"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="21"/>
       <c r="L132" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M132" s="14"/>
       <c r="N132" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O132" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P132" s="14"/>
       <c r="Q132" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R132" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S132" s="10"/>
       <c r="T132" s="10"/>
       <c r="U132" s="10"/>
     </row>
     <row r="133" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C133" s="17"/>
-      <c r="D133" s="17"/>
-      <c r="E133" s="23"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="18"/>
-      <c r="H133" s="18"/>
-      <c r="I133" s="22"/>
-      <c r="J133" s="17"/>
+      <c r="C133" s="21"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="25"/>
+      <c r="G133" s="25"/>
+      <c r="H133" s="25"/>
+      <c r="I133" s="26"/>
+      <c r="J133" s="21"/>
       <c r="L133" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M133" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
@@ -5524,42 +5524,42 @@
     </row>
     <row r="135" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C135" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D135" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E135" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F135" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G135" s="17"/>
-      <c r="H135" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I135" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J135" s="17"/>
+      <c r="E135" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="21"/>
+      <c r="H135" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I135" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J135" s="21"/>
       <c r="L135" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M135" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -5571,62 +5571,62 @@
       <c r="B136">
         <v>13</v>
       </c>
-      <c r="C136" s="17"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="23"/>
-      <c r="F136" s="22"/>
-      <c r="G136" s="17"/>
-      <c r="H136" s="17"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="17"/>
+      <c r="C136" s="21"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="21"/>
+      <c r="H136" s="21"/>
+      <c r="I136" s="24"/>
+      <c r="J136" s="21"/>
       <c r="L136" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M136" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N136" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O136" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P136" s="11">
         <v>0</v>
       </c>
       <c r="Q136" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R136" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S136" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T136" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V136" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C137" s="17"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="23"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="17"/>
-      <c r="H137" s="17"/>
-      <c r="I137" s="26"/>
-      <c r="J137" s="17"/>
+      <c r="C137" s="21"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="21"/>
+      <c r="H137" s="21"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="21"/>
       <c r="L137" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M137" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N137" s="10"/>
       <c r="O137" s="10"/>
@@ -5634,36 +5634,36 @@
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
       <c r="S137" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T137" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V137" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="138" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C138" s="17"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="23"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="17"/>
-      <c r="H138" s="17"/>
-      <c r="I138" s="26"/>
-      <c r="J138" s="17"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="25"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="21"/>
       <c r="L138" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M138" s="14"/>
       <c r="N138" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O138" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P138" s="14"/>
       <c r="Q138" s="5">
@@ -5671,32 +5671,32 @@
         <v>2496</v>
       </c>
       <c r="R138" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S138" s="10"/>
       <c r="T138" s="10"/>
       <c r="U138" s="10"/>
     </row>
     <row r="139" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C139" s="17"/>
-      <c r="D139" s="18"/>
-      <c r="E139" s="23"/>
-      <c r="F139" s="22"/>
-      <c r="G139" s="17"/>
-      <c r="H139" s="17"/>
-      <c r="I139" s="26"/>
-      <c r="J139" s="17"/>
+      <c r="C139" s="21"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="22"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+      <c r="I139" s="24"/>
+      <c r="J139" s="21"/>
       <c r="L139" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M139" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N139" s="10"/>
       <c r="O139" s="10"/>
       <c r="P139" s="10"/>
       <c r="Q139" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R139" s="10"/>
       <c r="S139" s="10"/>
@@ -5704,40 +5704,40 @@
       <c r="U139" s="10"/>
     </row>
     <row r="140" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C140" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D140" s="17"/>
-      <c r="E140" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G140" s="17"/>
-      <c r="H140" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I140" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J140" s="22" t="s">
-        <v>27</v>
+      <c r="C140" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I140" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J140" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L140" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N140" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O140" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P140" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q140" s="10"/>
       <c r="R140" s="10"/>
@@ -5746,62 +5746,62 @@
       <c r="U140" s="10"/>
     </row>
     <row r="141" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C141" s="17"/>
-      <c r="D141" s="17"/>
-      <c r="E141" s="17"/>
-      <c r="F141" s="17"/>
-      <c r="G141" s="17"/>
-      <c r="H141" s="17"/>
-      <c r="I141" s="18"/>
-      <c r="J141" s="22"/>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
+      <c r="I141" s="25"/>
+      <c r="J141" s="26"/>
       <c r="L141" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N141" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O141" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P141" s="11">
         <v>0</v>
       </c>
       <c r="Q141" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R141" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R141" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S141" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T141" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U141" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V141" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C142" s="17"/>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="17"/>
-      <c r="G142" s="17"/>
-      <c r="H142" s="17"/>
-      <c r="I142" s="18"/>
-      <c r="J142" s="22"/>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="25"/>
+      <c r="J142" s="26"/>
       <c r="L142" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M142" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N142" s="10"/>
       <c r="O142" s="10"/>
@@ -5809,62 +5809,62 @@
       <c r="Q142" s="10"/>
       <c r="R142" s="10"/>
       <c r="S142" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T142" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U142" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V142" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C143" s="17"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
-      <c r="G143" s="17"/>
-      <c r="H143" s="17"/>
-      <c r="I143" s="18"/>
-      <c r="J143" s="22"/>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="26"/>
       <c r="L143" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M143" s="14"/>
       <c r="N143" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O143" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P143" s="14"/>
       <c r="Q143" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R143" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S143" s="10"/>
       <c r="T143" s="10"/>
       <c r="U143" s="10"/>
     </row>
     <row r="144" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C144" s="17"/>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="17"/>
-      <c r="G144" s="17"/>
-      <c r="H144" s="17"/>
-      <c r="I144" s="18"/>
-      <c r="J144" s="22"/>
+      <c r="C144" s="21"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21"/>
+      <c r="I144" s="25"/>
+      <c r="J144" s="26"/>
       <c r="L144" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M144" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N144" s="10"/>
       <c r="O144" s="10"/>
@@ -5877,44 +5877,44 @@
     </row>
     <row r="145" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B145" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C145" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E145" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D145" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E145" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F145" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G145" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H145" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I145" s="17"/>
-      <c r="J145" s="27" t="s">
-        <v>34</v>
+      <c r="F145" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I145" s="21"/>
+      <c r="J145" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L145" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -5926,65 +5926,65 @@
       <c r="B146">
         <v>14</v>
       </c>
-      <c r="C146" s="17"/>
-      <c r="D146" s="23"/>
-      <c r="E146" s="18"/>
-      <c r="F146" s="17"/>
-      <c r="G146" s="22"/>
-      <c r="H146" s="17"/>
-      <c r="I146" s="17"/>
-      <c r="J146" s="27"/>
+      <c r="C146" s="21"/>
+      <c r="D146" s="22"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="21"/>
+      <c r="G146" s="26"/>
+      <c r="H146" s="21"/>
+      <c r="I146" s="21"/>
+      <c r="J146" s="20"/>
       <c r="L146" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M146" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N146" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O146" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P146" s="11">
         <v>0</v>
       </c>
       <c r="Q146" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R146" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S146" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T146" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U146" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V146" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B147" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C147" s="17"/>
-      <c r="D147" s="23"/>
-      <c r="E147" s="18"/>
-      <c r="F147" s="17"/>
-      <c r="G147" s="22"/>
-      <c r="H147" s="17"/>
-      <c r="I147" s="17"/>
-      <c r="J147" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C147" s="21"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="21"/>
+      <c r="G147" s="26"/>
+      <c r="H147" s="21"/>
+      <c r="I147" s="21"/>
+      <c r="J147" s="20"/>
       <c r="L147" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M147" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N147" s="10"/>
       <c r="O147" s="10"/>
@@ -5992,30 +5992,30 @@
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
       <c r="S147" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T147" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U147" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V147" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="148" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B148">
         <v>5</v>
       </c>
-      <c r="C148" s="17"/>
-      <c r="D148" s="23"/>
-      <c r="E148" s="18"/>
-      <c r="F148" s="17"/>
-      <c r="G148" s="22"/>
-      <c r="H148" s="17"/>
-      <c r="I148" s="17"/>
-      <c r="J148" s="27"/>
+      <c r="C148" s="21"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="21"/>
+      <c r="G148" s="26"/>
+      <c r="H148" s="21"/>
+      <c r="I148" s="21"/>
+      <c r="J148" s="20"/>
       <c r="L148" s="14" t="s">
         <v>17</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>960</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P148" s="14"/>
       <c r="Q148" s="5">
@@ -6033,34 +6033,34 @@
         <v>2688</v>
       </c>
       <c r="R148" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S148" s="10"/>
       <c r="T148" s="10"/>
       <c r="U148" s="10"/>
     </row>
     <row r="149" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C149" s="17"/>
-      <c r="D149" s="23"/>
-      <c r="E149" s="18"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="22"/>
-      <c r="H149" s="17"/>
-      <c r="I149" s="17"/>
-      <c r="J149" s="27"/>
+      <c r="C149" s="21"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="21"/>
+      <c r="G149" s="26"/>
+      <c r="H149" s="21"/>
+      <c r="I149" s="21"/>
+      <c r="J149" s="20"/>
       <c r="L149" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M149" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O149" s="10"/>
       <c r="P149" s="10"/>
       <c r="Q149" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R149" s="10"/>
       <c r="S149" s="10"/>
@@ -6068,40 +6068,40 @@
       <c r="U149" s="10"/>
     </row>
     <row r="150" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C150" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D150" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E150" s="23"/>
-      <c r="F150" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G150" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H150" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I150" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J150" s="23"/>
+      <c r="C150" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D150" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E150" s="22"/>
+      <c r="F150" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G150" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H150" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I150" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J150" s="22"/>
       <c r="L150" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N150" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O150" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P150" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q150" s="10"/>
       <c r="R150" s="10"/>
@@ -6110,62 +6110,62 @@
       <c r="U150" s="10"/>
     </row>
     <row r="151" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C151" s="17"/>
-      <c r="D151" s="17"/>
-      <c r="E151" s="23"/>
-      <c r="F151" s="18"/>
-      <c r="G151" s="18"/>
-      <c r="H151" s="18"/>
-      <c r="I151" s="22"/>
-      <c r="J151" s="23"/>
+      <c r="C151" s="21"/>
+      <c r="D151" s="21"/>
+      <c r="E151" s="22"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="26"/>
+      <c r="J151" s="22"/>
       <c r="L151" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M151" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N151" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O151" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P151" s="11">
         <v>1</v>
       </c>
       <c r="Q151" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R151" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S151" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S151" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T151" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U151" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V151" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C152" s="17"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="23"/>
-      <c r="F152" s="18"/>
-      <c r="G152" s="18"/>
-      <c r="H152" s="18"/>
-      <c r="I152" s="22"/>
-      <c r="J152" s="23"/>
+      <c r="C152" s="21"/>
+      <c r="D152" s="21"/>
+      <c r="E152" s="22"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
+      <c r="H152" s="25"/>
+      <c r="I152" s="26"/>
+      <c r="J152" s="22"/>
       <c r="L152" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M152" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N152" s="10"/>
       <c r="O152" s="10"/>
@@ -6173,62 +6173,62 @@
       <c r="Q152" s="10"/>
       <c r="R152" s="10"/>
       <c r="S152" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T152" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U152" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V152" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C153" s="17"/>
-      <c r="D153" s="17"/>
-      <c r="E153" s="23"/>
-      <c r="F153" s="18"/>
-      <c r="G153" s="18"/>
-      <c r="H153" s="18"/>
-      <c r="I153" s="22"/>
-      <c r="J153" s="23"/>
+      <c r="C153" s="21"/>
+      <c r="D153" s="21"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="25"/>
+      <c r="H153" s="25"/>
+      <c r="I153" s="26"/>
+      <c r="J153" s="22"/>
       <c r="L153" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M153" s="14"/>
       <c r="N153" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O153" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P153" s="14"/>
       <c r="Q153" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R153" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S153" s="10"/>
       <c r="T153" s="10"/>
       <c r="U153" s="10"/>
     </row>
     <row r="154" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C154" s="17"/>
-      <c r="D154" s="17"/>
-      <c r="E154" s="23"/>
-      <c r="F154" s="18"/>
-      <c r="G154" s="18"/>
-      <c r="H154" s="18"/>
-      <c r="I154" s="22"/>
-      <c r="J154" s="23"/>
+      <c r="C154" s="21"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="22"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
+      <c r="H154" s="25"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="22"/>
       <c r="L154" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M154" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N154" s="10"/>
       <c r="O154" s="10"/>
@@ -6246,50 +6246,50 @@
       <c r="P156" s="10"/>
     </row>
     <row r="157" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="B157" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C157" s="28"/>
+      <c r="B157" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C157" s="27"/>
       <c r="P157" s="10"/>
     </row>
     <row r="158" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B158" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C158" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D158" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D158" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E158" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F158" s="22"/>
-      <c r="G158" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H158" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="I158" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J158" s="17"/>
+      <c r="E158" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F158" s="26"/>
+      <c r="G158" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H158" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I158" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J158" s="21"/>
       <c r="L158" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M158" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N158" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O158" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P158" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q158" s="10"/>
       <c r="R158" s="10"/>
@@ -6301,62 +6301,62 @@
       <c r="B159">
         <v>15</v>
       </c>
-      <c r="C159" s="17"/>
-      <c r="D159" s="18"/>
-      <c r="E159" s="23"/>
-      <c r="F159" s="22"/>
-      <c r="G159" s="17"/>
-      <c r="H159" s="22"/>
-      <c r="I159" s="26"/>
-      <c r="J159" s="17"/>
+      <c r="C159" s="21"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="22"/>
+      <c r="F159" s="26"/>
+      <c r="G159" s="21"/>
+      <c r="H159" s="26"/>
+      <c r="I159" s="24"/>
+      <c r="J159" s="21"/>
       <c r="L159" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M159" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N159" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O159" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P159" s="11">
         <v>0</v>
       </c>
       <c r="Q159" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R159" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S159" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T159" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U159" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V159" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="160" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C160" s="17"/>
-      <c r="D160" s="18"/>
-      <c r="E160" s="23"/>
-      <c r="F160" s="22"/>
-      <c r="G160" s="17"/>
-      <c r="H160" s="22"/>
-      <c r="I160" s="26"/>
-      <c r="J160" s="17"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="25"/>
+      <c r="E160" s="22"/>
+      <c r="F160" s="26"/>
+      <c r="G160" s="21"/>
+      <c r="H160" s="26"/>
+      <c r="I160" s="24"/>
+      <c r="J160" s="21"/>
       <c r="L160" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M160" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N160" s="10"/>
       <c r="O160" s="10"/>
@@ -6364,36 +6364,36 @@
       <c r="Q160" s="10"/>
       <c r="R160" s="10"/>
       <c r="S160" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T160" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U160" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V160" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C161" s="17"/>
-      <c r="D161" s="18"/>
-      <c r="E161" s="23"/>
-      <c r="F161" s="22"/>
-      <c r="G161" s="17"/>
-      <c r="H161" s="22"/>
-      <c r="I161" s="26"/>
-      <c r="J161" s="17"/>
+      <c r="C161" s="21"/>
+      <c r="D161" s="25"/>
+      <c r="E161" s="22"/>
+      <c r="F161" s="26"/>
+      <c r="G161" s="21"/>
+      <c r="H161" s="26"/>
+      <c r="I161" s="24"/>
+      <c r="J161" s="21"/>
       <c r="L161" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M161" s="14"/>
       <c r="N161" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P161" s="14"/>
       <c r="Q161" s="5">
@@ -6401,32 +6401,32 @@
         <v>2880</v>
       </c>
       <c r="R161" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S161" s="10"/>
       <c r="T161" s="10"/>
       <c r="U161" s="10"/>
     </row>
     <row r="162" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C162" s="17"/>
-      <c r="D162" s="18"/>
-      <c r="E162" s="23"/>
-      <c r="F162" s="22"/>
-      <c r="G162" s="17"/>
-      <c r="H162" s="22"/>
-      <c r="I162" s="26"/>
-      <c r="J162" s="17"/>
+      <c r="C162" s="21"/>
+      <c r="D162" s="25"/>
+      <c r="E162" s="22"/>
+      <c r="F162" s="26"/>
+      <c r="G162" s="21"/>
+      <c r="H162" s="26"/>
+      <c r="I162" s="24"/>
+      <c r="J162" s="21"/>
       <c r="L162" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M162" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N162" s="10"/>
       <c r="O162" s="10"/>
       <c r="P162" s="10"/>
       <c r="Q162" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R162" s="10"/>
       <c r="S162" s="10"/>
@@ -6434,40 +6434,40 @@
       <c r="U162" s="10"/>
     </row>
     <row r="163" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C163" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D163" s="17"/>
-      <c r="E163" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F163" s="17"/>
-      <c r="G163" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H163" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I163" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J163" s="22" t="s">
-        <v>27</v>
+      <c r="C163" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D163" s="21"/>
+      <c r="E163" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F163" s="21"/>
+      <c r="G163" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H163" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I163" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J163" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L163" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -6476,62 +6476,62 @@
       <c r="U163" s="10"/>
     </row>
     <row r="164" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C164" s="17"/>
-      <c r="D164" s="17"/>
-      <c r="E164" s="17"/>
-      <c r="F164" s="17"/>
-      <c r="G164" s="17"/>
-      <c r="H164" s="17"/>
-      <c r="I164" s="18"/>
-      <c r="J164" s="22"/>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
+      <c r="E164" s="21"/>
+      <c r="F164" s="21"/>
+      <c r="G164" s="21"/>
+      <c r="H164" s="21"/>
+      <c r="I164" s="25"/>
+      <c r="J164" s="26"/>
       <c r="L164" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M164" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N164" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O164" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P164" s="11">
         <v>0</v>
       </c>
       <c r="Q164" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R164" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R164" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S164" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T164" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U164" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V164" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C165" s="17"/>
-      <c r="D165" s="17"/>
-      <c r="E165" s="17"/>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17"/>
-      <c r="H165" s="17"/>
-      <c r="I165" s="18"/>
-      <c r="J165" s="22"/>
+      <c r="C165" s="21"/>
+      <c r="D165" s="21"/>
+      <c r="E165" s="21"/>
+      <c r="F165" s="21"/>
+      <c r="G165" s="21"/>
+      <c r="H165" s="21"/>
+      <c r="I165" s="25"/>
+      <c r="J165" s="26"/>
       <c r="L165" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M165" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N165" s="10"/>
       <c r="O165" s="10"/>
@@ -6539,62 +6539,62 @@
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
       <c r="S165" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T165" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U165" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V165" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="166" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C166" s="17"/>
-      <c r="D166" s="17"/>
-      <c r="E166" s="17"/>
-      <c r="F166" s="17"/>
-      <c r="G166" s="17"/>
-      <c r="H166" s="17"/>
-      <c r="I166" s="18"/>
-      <c r="J166" s="22"/>
+      <c r="C166" s="21"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
+      <c r="I166" s="25"/>
+      <c r="J166" s="26"/>
       <c r="L166" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M166" s="14"/>
       <c r="N166" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P166" s="14"/>
       <c r="Q166" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R166" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S166" s="10"/>
       <c r="T166" s="10"/>
       <c r="U166" s="10"/>
     </row>
     <row r="167" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C167" s="17"/>
-      <c r="D167" s="17"/>
-      <c r="E167" s="17"/>
-      <c r="F167" s="17"/>
-      <c r="G167" s="17"/>
-      <c r="H167" s="17"/>
-      <c r="I167" s="18"/>
-      <c r="J167" s="22"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
+      <c r="I167" s="25"/>
+      <c r="J167" s="26"/>
       <c r="L167" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M167" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N167" s="10"/>
       <c r="O167" s="10"/>
@@ -6606,40 +6606,40 @@
       <c r="U167" s="10"/>
     </row>
     <row r="168" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C168" s="17" t="s">
+      <c r="C168" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D168" s="21"/>
+      <c r="E168" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D168" s="17"/>
-      <c r="E168" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F168" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="G168" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H168" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I168" s="17"/>
-      <c r="J168" s="27" t="s">
-        <v>34</v>
+      <c r="F168" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G168" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H168" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I168" s="21"/>
+      <c r="J168" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L168" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N168" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O168" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P168" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q168" s="10"/>
       <c r="R168" s="10"/>
@@ -6648,65 +6648,65 @@
       <c r="U168" s="10"/>
     </row>
     <row r="169" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C169" s="17"/>
-      <c r="D169" s="17"/>
-      <c r="E169" s="18"/>
-      <c r="F169" s="22"/>
-      <c r="G169" s="30"/>
-      <c r="H169" s="30"/>
-      <c r="I169" s="17"/>
-      <c r="J169" s="27"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="21"/>
+      <c r="E169" s="25"/>
+      <c r="F169" s="26"/>
+      <c r="G169" s="18"/>
+      <c r="H169" s="18"/>
+      <c r="I169" s="21"/>
+      <c r="J169" s="20"/>
       <c r="L169" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M169" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N169" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O169" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P169" s="11">
         <v>0</v>
       </c>
       <c r="Q169" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R169" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S169" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T169" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U169" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V169" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="170" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B170" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C170" s="17"/>
-      <c r="D170" s="17"/>
-      <c r="E170" s="18"/>
-      <c r="F170" s="22"/>
-      <c r="G170" s="30"/>
-      <c r="H170" s="30"/>
-      <c r="I170" s="17"/>
-      <c r="J170" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C170" s="21"/>
+      <c r="D170" s="21"/>
+      <c r="E170" s="25"/>
+      <c r="F170" s="26"/>
+      <c r="G170" s="18"/>
+      <c r="H170" s="18"/>
+      <c r="I170" s="21"/>
+      <c r="J170" s="20"/>
       <c r="L170" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N170" s="10"/>
       <c r="O170" s="10"/>
@@ -6714,30 +6714,30 @@
       <c r="Q170" s="10"/>
       <c r="R170" s="10"/>
       <c r="S170" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T170" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U170" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V170" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B171">
         <v>6</v>
       </c>
-      <c r="C171" s="17"/>
-      <c r="D171" s="17"/>
-      <c r="E171" s="18"/>
-      <c r="F171" s="22"/>
-      <c r="G171" s="30"/>
-      <c r="H171" s="30"/>
-      <c r="I171" s="17"/>
-      <c r="J171" s="27"/>
+      <c r="C171" s="21"/>
+      <c r="D171" s="21"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="26"/>
+      <c r="G171" s="18"/>
+      <c r="H171" s="18"/>
+      <c r="I171" s="21"/>
+      <c r="J171" s="20"/>
       <c r="L171" s="14" t="s">
         <v>17</v>
       </c>
@@ -6747,36 +6747,36 @@
         <v>1152</v>
       </c>
       <c r="O171" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P171" s="14"/>
       <c r="Q171" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R171" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S171" s="10"/>
       <c r="T171" s="10"/>
       <c r="U171" s="10"/>
     </row>
     <row r="172" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C172" s="17"/>
-      <c r="D172" s="17"/>
-      <c r="E172" s="18"/>
-      <c r="F172" s="22"/>
-      <c r="G172" s="31"/>
-      <c r="H172" s="31"/>
-      <c r="I172" s="17"/>
-      <c r="J172" s="27"/>
+      <c r="C172" s="21"/>
+      <c r="D172" s="21"/>
+      <c r="E172" s="25"/>
+      <c r="F172" s="26"/>
+      <c r="G172" s="19"/>
+      <c r="H172" s="19"/>
+      <c r="I172" s="21"/>
+      <c r="J172" s="20"/>
       <c r="L172" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M172" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N172" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O172" s="10"/>
       <c r="P172" s="10"/>
@@ -6787,38 +6787,38 @@
       <c r="U172" s="10"/>
     </row>
     <row r="173" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C173" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D173" s="17"/>
-      <c r="E173" s="23"/>
-      <c r="F173" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G173" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H173" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I173" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J173" s="17"/>
+      <c r="C173" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D173" s="21"/>
+      <c r="E173" s="22"/>
+      <c r="F173" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G173" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="H173" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I173" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J173" s="21"/>
       <c r="L173" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M173" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -6827,62 +6827,62 @@
       <c r="U173" s="10"/>
     </row>
     <row r="174" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C174" s="17"/>
-      <c r="D174" s="17"/>
-      <c r="E174" s="23"/>
-      <c r="F174" s="18"/>
-      <c r="G174" s="18"/>
-      <c r="H174" s="18"/>
-      <c r="I174" s="22"/>
-      <c r="J174" s="17"/>
+      <c r="C174" s="21"/>
+      <c r="D174" s="21"/>
+      <c r="E174" s="22"/>
+      <c r="F174" s="25"/>
+      <c r="G174" s="25"/>
+      <c r="H174" s="25"/>
+      <c r="I174" s="26"/>
+      <c r="J174" s="21"/>
       <c r="L174" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M174" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N174" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O174" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P174" s="11">
         <v>1</v>
       </c>
       <c r="Q174" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R174" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S174" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="S174" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="T174" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U174" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V174" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C175" s="17"/>
-      <c r="D175" s="17"/>
-      <c r="E175" s="23"/>
-      <c r="F175" s="18"/>
-      <c r="G175" s="18"/>
-      <c r="H175" s="18"/>
-      <c r="I175" s="22"/>
-      <c r="J175" s="17"/>
+      <c r="C175" s="21"/>
+      <c r="D175" s="21"/>
+      <c r="E175" s="22"/>
+      <c r="F175" s="25"/>
+      <c r="G175" s="25"/>
+      <c r="H175" s="25"/>
+      <c r="I175" s="26"/>
+      <c r="J175" s="21"/>
       <c r="L175" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N175" s="10"/>
       <c r="O175" s="10"/>
@@ -6890,62 +6890,62 @@
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
       <c r="S175" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T175" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U175" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V175" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="176" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C176" s="17"/>
-      <c r="D176" s="17"/>
-      <c r="E176" s="23"/>
-      <c r="F176" s="18"/>
-      <c r="G176" s="18"/>
-      <c r="H176" s="18"/>
-      <c r="I176" s="22"/>
-      <c r="J176" s="17"/>
+      <c r="C176" s="21"/>
+      <c r="D176" s="21"/>
+      <c r="E176" s="22"/>
+      <c r="F176" s="25"/>
+      <c r="G176" s="25"/>
+      <c r="H176" s="25"/>
+      <c r="I176" s="26"/>
+      <c r="J176" s="21"/>
       <c r="L176" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M176" s="14"/>
       <c r="N176" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O176" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P176" s="14"/>
       <c r="Q176" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R176" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S176" s="10"/>
       <c r="T176" s="10"/>
       <c r="U176" s="10"/>
     </row>
     <row r="177" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C177" s="17"/>
-      <c r="D177" s="17"/>
-      <c r="E177" s="23"/>
-      <c r="F177" s="18"/>
-      <c r="G177" s="18"/>
-      <c r="H177" s="18"/>
-      <c r="I177" s="22"/>
-      <c r="J177" s="17"/>
+      <c r="C177" s="21"/>
+      <c r="D177" s="21"/>
+      <c r="E177" s="22"/>
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25"/>
+      <c r="I177" s="26"/>
+      <c r="J177" s="21"/>
       <c r="L177" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M177" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N177" s="10"/>
       <c r="O177" s="10"/>
@@ -6960,32 +6960,32 @@
       <c r="P178" s="10"/>
     </row>
     <row r="179" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C179" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D179" s="17"/>
-      <c r="E179" s="23"/>
-      <c r="F179" s="23"/>
-      <c r="G179" s="17"/>
-      <c r="H179" s="17"/>
-      <c r="I179" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="J179" s="17"/>
+      <c r="C179" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D179" s="21"/>
+      <c r="E179" s="22"/>
+      <c r="F179" s="22"/>
+      <c r="G179" s="21"/>
+      <c r="H179" s="21"/>
+      <c r="I179" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J179" s="21"/>
       <c r="L179" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -6994,62 +6994,62 @@
       <c r="U179" s="10"/>
     </row>
     <row r="180" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C180" s="17"/>
-      <c r="D180" s="17"/>
-      <c r="E180" s="23"/>
-      <c r="F180" s="23"/>
-      <c r="G180" s="17"/>
-      <c r="H180" s="17"/>
-      <c r="I180" s="26"/>
-      <c r="J180" s="17"/>
+      <c r="C180" s="21"/>
+      <c r="D180" s="21"/>
+      <c r="E180" s="22"/>
+      <c r="F180" s="22"/>
+      <c r="G180" s="21"/>
+      <c r="H180" s="21"/>
+      <c r="I180" s="24"/>
+      <c r="J180" s="21"/>
       <c r="L180" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P180" s="11">
         <v>0</v>
       </c>
       <c r="Q180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V180" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C181" s="17"/>
-      <c r="D181" s="17"/>
-      <c r="E181" s="23"/>
-      <c r="F181" s="23"/>
-      <c r="G181" s="17"/>
-      <c r="H181" s="17"/>
-      <c r="I181" s="26"/>
-      <c r="J181" s="17"/>
+      <c r="C181" s="21"/>
+      <c r="D181" s="21"/>
+      <c r="E181" s="22"/>
+      <c r="F181" s="22"/>
+      <c r="G181" s="21"/>
+      <c r="H181" s="21"/>
+      <c r="I181" s="24"/>
+      <c r="J181" s="21"/>
       <c r="L181" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N181" s="10"/>
       <c r="O181" s="10"/>
@@ -7062,49 +7062,49 @@
       <c r="V181" s="10"/>
     </row>
     <row r="182" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C182" s="17"/>
-      <c r="D182" s="17"/>
-      <c r="E182" s="23"/>
-      <c r="F182" s="23"/>
-      <c r="G182" s="17"/>
-      <c r="H182" s="17"/>
-      <c r="I182" s="26"/>
-      <c r="J182" s="17"/>
+      <c r="C182" s="21"/>
+      <c r="D182" s="21"/>
+      <c r="E182" s="22"/>
+      <c r="F182" s="22"/>
+      <c r="G182" s="21"/>
+      <c r="H182" s="21"/>
+      <c r="I182" s="24"/>
+      <c r="J182" s="21"/>
       <c r="L182" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M182" s="14"/>
       <c r="N182" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O182" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P182" s="14"/>
       <c r="Q182" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R182" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S182" s="10"/>
       <c r="T182" s="10"/>
       <c r="U182" s="10"/>
     </row>
     <row r="183" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C183" s="17"/>
-      <c r="D183" s="17"/>
-      <c r="E183" s="23"/>
-      <c r="F183" s="23"/>
-      <c r="G183" s="17"/>
-      <c r="H183" s="17"/>
-      <c r="I183" s="26"/>
-      <c r="J183" s="17"/>
+      <c r="C183" s="21"/>
+      <c r="D183" s="21"/>
+      <c r="E183" s="22"/>
+      <c r="F183" s="22"/>
+      <c r="G183" s="21"/>
+      <c r="H183" s="21"/>
+      <c r="I183" s="24"/>
+      <c r="J183" s="21"/>
       <c r="L183" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M183" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="10"/>
@@ -7116,34 +7116,34 @@
       <c r="U183" s="10"/>
     </row>
     <row r="184" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C184" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D184" s="17"/>
-      <c r="E184" s="23"/>
-      <c r="F184" s="23"/>
-      <c r="G184" s="17"/>
-      <c r="H184" s="17"/>
-      <c r="I184" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J184" s="22" t="s">
-        <v>27</v>
+      <c r="C184" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D184" s="21"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="21"/>
+      <c r="H184" s="21"/>
+      <c r="I184" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J184" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="L184" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M184" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N184" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O184" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P184" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q184" s="10"/>
       <c r="R184" s="10"/>
@@ -7152,62 +7152,62 @@
       <c r="U184" s="10"/>
     </row>
     <row r="185" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C185" s="17"/>
-      <c r="D185" s="17"/>
-      <c r="E185" s="23"/>
-      <c r="F185" s="23"/>
-      <c r="G185" s="17"/>
-      <c r="H185" s="17"/>
-      <c r="I185" s="18"/>
-      <c r="J185" s="22"/>
+      <c r="C185" s="21"/>
+      <c r="D185" s="21"/>
+      <c r="E185" s="22"/>
+      <c r="F185" s="22"/>
+      <c r="G185" s="21"/>
+      <c r="H185" s="21"/>
+      <c r="I185" s="25"/>
+      <c r="J185" s="26"/>
       <c r="L185" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M185" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N185" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O185" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P185" s="11">
         <v>0</v>
       </c>
       <c r="Q185" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="R185" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="R185" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="S185" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T185" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U185" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V185" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C186" s="17"/>
-      <c r="D186" s="17"/>
-      <c r="E186" s="23"/>
-      <c r="F186" s="23"/>
-      <c r="G186" s="17"/>
-      <c r="H186" s="17"/>
-      <c r="I186" s="18"/>
-      <c r="J186" s="22"/>
+      <c r="C186" s="21"/>
+      <c r="D186" s="21"/>
+      <c r="E186" s="22"/>
+      <c r="F186" s="22"/>
+      <c r="G186" s="21"/>
+      <c r="H186" s="21"/>
+      <c r="I186" s="25"/>
+      <c r="J186" s="26"/>
       <c r="L186" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N186" s="10"/>
       <c r="O186" s="10"/>
@@ -7215,62 +7215,62 @@
       <c r="Q186" s="10"/>
       <c r="R186" s="10"/>
       <c r="S186" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T186" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U186" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V186" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="187" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C187" s="17"/>
-      <c r="D187" s="17"/>
-      <c r="E187" s="23"/>
-      <c r="F187" s="23"/>
-      <c r="G187" s="17"/>
-      <c r="H187" s="17"/>
-      <c r="I187" s="18"/>
-      <c r="J187" s="22"/>
+      <c r="C187" s="21"/>
+      <c r="D187" s="21"/>
+      <c r="E187" s="22"/>
+      <c r="F187" s="22"/>
+      <c r="G187" s="21"/>
+      <c r="H187" s="21"/>
+      <c r="I187" s="25"/>
+      <c r="J187" s="26"/>
       <c r="L187" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M187" s="14"/>
       <c r="N187" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O187" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P187" s="14"/>
       <c r="Q187" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R187" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S187" s="10"/>
       <c r="T187" s="10"/>
       <c r="U187" s="10"/>
     </row>
     <row r="188" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C188" s="17"/>
-      <c r="D188" s="17"/>
-      <c r="E188" s="23"/>
-      <c r="F188" s="23"/>
-      <c r="G188" s="17"/>
-      <c r="H188" s="17"/>
-      <c r="I188" s="18"/>
-      <c r="J188" s="22"/>
+      <c r="C188" s="21"/>
+      <c r="D188" s="21"/>
+      <c r="E188" s="22"/>
+      <c r="F188" s="22"/>
+      <c r="G188" s="21"/>
+      <c r="H188" s="21"/>
+      <c r="I188" s="25"/>
+      <c r="J188" s="26"/>
       <c r="L188" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M188" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N188" s="10"/>
       <c r="O188" s="10"/>
@@ -7282,32 +7282,32 @@
       <c r="U188" s="10"/>
     </row>
     <row r="189" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C189" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D189" s="17"/>
-      <c r="E189" s="23"/>
-      <c r="F189" s="23"/>
-      <c r="G189" s="17"/>
-      <c r="H189" s="17"/>
-      <c r="I189" s="29"/>
-      <c r="J189" s="27" t="s">
-        <v>34</v>
+      <c r="C189" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D189" s="21"/>
+      <c r="E189" s="22"/>
+      <c r="F189" s="22"/>
+      <c r="G189" s="21"/>
+      <c r="H189" s="21"/>
+      <c r="I189" s="17"/>
+      <c r="J189" s="20" t="s">
+        <v>33</v>
       </c>
       <c r="L189" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M189" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -7316,65 +7316,65 @@
       <c r="U189" s="10"/>
     </row>
     <row r="190" spans="2:22" x14ac:dyDescent="0.45">
-      <c r="C190" s="17"/>
-      <c r="D190" s="17"/>
-      <c r="E190" s="23"/>
-      <c r="F190" s="23"/>
-      <c r="G190" s="17"/>
-      <c r="H190" s="17"/>
-      <c r="I190" s="30"/>
-      <c r="J190" s="27"/>
+      <c r="C190" s="21"/>
+      <c r="D190" s="21"/>
+      <c r="E190" s="22"/>
+      <c r="F190" s="22"/>
+      <c r="G190" s="21"/>
+      <c r="H190" s="21"/>
+      <c r="I190" s="18"/>
+      <c r="J190" s="20"/>
       <c r="L190" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P190" s="11">
         <v>0</v>
       </c>
       <c r="Q190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V190" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="191" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B191" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C191" s="17"/>
-      <c r="D191" s="17"/>
-      <c r="E191" s="23"/>
-      <c r="F191" s="23"/>
-      <c r="G191" s="17"/>
-      <c r="H191" s="17"/>
-      <c r="I191" s="30"/>
-      <c r="J191" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="C191" s="21"/>
+      <c r="D191" s="21"/>
+      <c r="E191" s="22"/>
+      <c r="F191" s="22"/>
+      <c r="G191" s="21"/>
+      <c r="H191" s="21"/>
+      <c r="I191" s="18"/>
+      <c r="J191" s="20"/>
       <c r="L191" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M191" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N191" s="10"/>
       <c r="O191" s="10"/>
@@ -7390,14 +7390,14 @@
       <c r="B192">
         <v>7</v>
       </c>
-      <c r="C192" s="17"/>
-      <c r="D192" s="17"/>
-      <c r="E192" s="23"/>
-      <c r="F192" s="23"/>
-      <c r="G192" s="17"/>
-      <c r="H192" s="17"/>
-      <c r="I192" s="30"/>
-      <c r="J192" s="27"/>
+      <c r="C192" s="21"/>
+      <c r="D192" s="21"/>
+      <c r="E192" s="22"/>
+      <c r="F192" s="22"/>
+      <c r="G192" s="21"/>
+      <c r="H192" s="21"/>
+      <c r="I192" s="18"/>
+      <c r="J192" s="20"/>
       <c r="L192" s="14" t="s">
         <v>17</v>
       </c>
@@ -7407,36 +7407,36 @@
         <v>1344</v>
       </c>
       <c r="O192" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P192" s="14"/>
       <c r="Q192" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R192" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S192" s="10"/>
       <c r="T192" s="10"/>
       <c r="U192" s="10"/>
     </row>
     <row r="193" spans="3:21" x14ac:dyDescent="0.45">
-      <c r="C193" s="17"/>
-      <c r="D193" s="17"/>
-      <c r="E193" s="23"/>
-      <c r="F193" s="23"/>
-      <c r="G193" s="17"/>
-      <c r="H193" s="17"/>
-      <c r="I193" s="31"/>
-      <c r="J193" s="27"/>
+      <c r="C193" s="21"/>
+      <c r="D193" s="21"/>
+      <c r="E193" s="22"/>
+      <c r="F193" s="22"/>
+      <c r="G193" s="21"/>
+      <c r="H193" s="21"/>
+      <c r="I193" s="19"/>
+      <c r="J193" s="20"/>
       <c r="L193" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M193" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P193" s="10"/>
       <c r="Q193" s="10"/>
@@ -7447,6 +7447,263 @@
     </row>
   </sheetData>
   <mergeCells count="281">
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="D44:D48"/>
+    <mergeCell ref="E44:E48"/>
+    <mergeCell ref="F44:F48"/>
+    <mergeCell ref="G44:G48"/>
+    <mergeCell ref="H44:H48"/>
+    <mergeCell ref="I44:I48"/>
+    <mergeCell ref="J44:J48"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="I55:I59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="J60:J64"/>
+    <mergeCell ref="C65:C69"/>
+    <mergeCell ref="D65:D69"/>
+    <mergeCell ref="E65:E69"/>
+    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="G65:G69"/>
+    <mergeCell ref="H65:H69"/>
+    <mergeCell ref="I65:I69"/>
+    <mergeCell ref="J65:J69"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="D60:D64"/>
+    <mergeCell ref="E60:E64"/>
+    <mergeCell ref="F60:F64"/>
+    <mergeCell ref="G60:G64"/>
+    <mergeCell ref="H60:H64"/>
+    <mergeCell ref="I71:I75"/>
+    <mergeCell ref="J71:J75"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="E76:E80"/>
+    <mergeCell ref="F76:F80"/>
+    <mergeCell ref="G76:G80"/>
+    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="I76:I80"/>
+    <mergeCell ref="J76:J80"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="I81:I85"/>
+    <mergeCell ref="J81:J85"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="D86:D90"/>
+    <mergeCell ref="E86:E90"/>
+    <mergeCell ref="F86:F90"/>
+    <mergeCell ref="G86:G90"/>
+    <mergeCell ref="H86:H90"/>
+    <mergeCell ref="I86:I90"/>
+    <mergeCell ref="J86:J90"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="E81:E85"/>
+    <mergeCell ref="F81:F85"/>
+    <mergeCell ref="G81:G85"/>
+    <mergeCell ref="H81:H85"/>
+    <mergeCell ref="I93:I97"/>
+    <mergeCell ref="J93:J97"/>
+    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="D98:D102"/>
+    <mergeCell ref="E98:E102"/>
+    <mergeCell ref="F98:F102"/>
+    <mergeCell ref="G98:G102"/>
+    <mergeCell ref="H98:H102"/>
+    <mergeCell ref="I98:I102"/>
+    <mergeCell ref="J98:J102"/>
+    <mergeCell ref="C93:C97"/>
+    <mergeCell ref="D93:D97"/>
+    <mergeCell ref="E93:E97"/>
+    <mergeCell ref="F93:F97"/>
+    <mergeCell ref="G93:G97"/>
+    <mergeCell ref="H93:H97"/>
+    <mergeCell ref="I103:I107"/>
+    <mergeCell ref="J103:J107"/>
+    <mergeCell ref="C108:C112"/>
+    <mergeCell ref="D108:D112"/>
+    <mergeCell ref="E108:E112"/>
+    <mergeCell ref="F108:F112"/>
+    <mergeCell ref="G108:G112"/>
+    <mergeCell ref="H108:H112"/>
+    <mergeCell ref="I108:I112"/>
+    <mergeCell ref="J108:J112"/>
+    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="D103:D107"/>
+    <mergeCell ref="E103:E107"/>
+    <mergeCell ref="F103:F107"/>
+    <mergeCell ref="G103:G107"/>
+    <mergeCell ref="H103:H107"/>
+    <mergeCell ref="I114:I118"/>
+    <mergeCell ref="J114:J118"/>
+    <mergeCell ref="C119:C123"/>
+    <mergeCell ref="D119:D123"/>
+    <mergeCell ref="E119:E123"/>
+    <mergeCell ref="F119:F123"/>
+    <mergeCell ref="G119:G123"/>
+    <mergeCell ref="H119:H123"/>
+    <mergeCell ref="I119:I123"/>
+    <mergeCell ref="J119:J123"/>
+    <mergeCell ref="C114:C118"/>
+    <mergeCell ref="D114:D118"/>
+    <mergeCell ref="E114:E118"/>
+    <mergeCell ref="F114:F118"/>
+    <mergeCell ref="G114:G118"/>
+    <mergeCell ref="H114:H118"/>
+    <mergeCell ref="I124:I128"/>
+    <mergeCell ref="J124:J128"/>
+    <mergeCell ref="C129:C133"/>
+    <mergeCell ref="D129:D133"/>
+    <mergeCell ref="E129:E133"/>
+    <mergeCell ref="F129:F133"/>
+    <mergeCell ref="G129:G133"/>
+    <mergeCell ref="H129:H133"/>
+    <mergeCell ref="I129:I133"/>
+    <mergeCell ref="J129:J133"/>
+    <mergeCell ref="C124:C128"/>
+    <mergeCell ref="D124:D128"/>
+    <mergeCell ref="E124:E128"/>
+    <mergeCell ref="F124:F128"/>
+    <mergeCell ref="G124:G128"/>
+    <mergeCell ref="H124:H128"/>
+    <mergeCell ref="I135:I139"/>
+    <mergeCell ref="J135:J139"/>
+    <mergeCell ref="C140:C144"/>
+    <mergeCell ref="D140:D144"/>
+    <mergeCell ref="E140:E144"/>
+    <mergeCell ref="F140:F144"/>
+    <mergeCell ref="G140:G144"/>
+    <mergeCell ref="H140:H144"/>
+    <mergeCell ref="I140:I144"/>
+    <mergeCell ref="J140:J144"/>
+    <mergeCell ref="C135:C139"/>
+    <mergeCell ref="D135:D139"/>
+    <mergeCell ref="E135:E139"/>
+    <mergeCell ref="F135:F139"/>
+    <mergeCell ref="G135:G139"/>
+    <mergeCell ref="H135:H139"/>
+    <mergeCell ref="I145:I149"/>
+    <mergeCell ref="J145:J149"/>
+    <mergeCell ref="C150:C154"/>
+    <mergeCell ref="D150:D154"/>
+    <mergeCell ref="E150:E154"/>
+    <mergeCell ref="F150:F154"/>
+    <mergeCell ref="G150:G154"/>
+    <mergeCell ref="H150:H154"/>
+    <mergeCell ref="I150:I154"/>
+    <mergeCell ref="J150:J154"/>
+    <mergeCell ref="C145:C149"/>
+    <mergeCell ref="D145:D149"/>
+    <mergeCell ref="E145:E149"/>
+    <mergeCell ref="F145:F149"/>
+    <mergeCell ref="G145:G149"/>
+    <mergeCell ref="H145:H149"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="I158:I162"/>
+    <mergeCell ref="J158:J162"/>
+    <mergeCell ref="C163:C167"/>
+    <mergeCell ref="D163:D167"/>
+    <mergeCell ref="E163:E167"/>
+    <mergeCell ref="F163:F167"/>
+    <mergeCell ref="G163:G167"/>
+    <mergeCell ref="H163:H167"/>
+    <mergeCell ref="I163:I167"/>
+    <mergeCell ref="J163:J167"/>
+    <mergeCell ref="C158:C162"/>
+    <mergeCell ref="D158:D162"/>
+    <mergeCell ref="E158:E162"/>
+    <mergeCell ref="F158:F162"/>
+    <mergeCell ref="G158:G162"/>
+    <mergeCell ref="H158:H162"/>
+    <mergeCell ref="I168:I172"/>
+    <mergeCell ref="J168:J172"/>
+    <mergeCell ref="C173:C177"/>
+    <mergeCell ref="D173:D177"/>
+    <mergeCell ref="E173:E177"/>
+    <mergeCell ref="F173:F177"/>
+    <mergeCell ref="G173:G177"/>
+    <mergeCell ref="H173:H177"/>
+    <mergeCell ref="I173:I177"/>
+    <mergeCell ref="J173:J177"/>
+    <mergeCell ref="C168:C172"/>
+    <mergeCell ref="D168:D172"/>
+    <mergeCell ref="E168:E172"/>
+    <mergeCell ref="F168:F172"/>
+    <mergeCell ref="G168:G172"/>
+    <mergeCell ref="H168:H172"/>
     <mergeCell ref="I189:I193"/>
     <mergeCell ref="J189:J193"/>
     <mergeCell ref="C189:C193"/>
@@ -7471,263 +7728,6 @@
     <mergeCell ref="F179:F183"/>
     <mergeCell ref="G179:G183"/>
     <mergeCell ref="H179:H183"/>
-    <mergeCell ref="I168:I172"/>
-    <mergeCell ref="J168:J172"/>
-    <mergeCell ref="C173:C177"/>
-    <mergeCell ref="D173:D177"/>
-    <mergeCell ref="E173:E177"/>
-    <mergeCell ref="F173:F177"/>
-    <mergeCell ref="G173:G177"/>
-    <mergeCell ref="H173:H177"/>
-    <mergeCell ref="I173:I177"/>
-    <mergeCell ref="J173:J177"/>
-    <mergeCell ref="C168:C172"/>
-    <mergeCell ref="D168:D172"/>
-    <mergeCell ref="E168:E172"/>
-    <mergeCell ref="F168:F172"/>
-    <mergeCell ref="G168:G172"/>
-    <mergeCell ref="H168:H172"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="I158:I162"/>
-    <mergeCell ref="J158:J162"/>
-    <mergeCell ref="C163:C167"/>
-    <mergeCell ref="D163:D167"/>
-    <mergeCell ref="E163:E167"/>
-    <mergeCell ref="F163:F167"/>
-    <mergeCell ref="G163:G167"/>
-    <mergeCell ref="H163:H167"/>
-    <mergeCell ref="I163:I167"/>
-    <mergeCell ref="J163:J167"/>
-    <mergeCell ref="C158:C162"/>
-    <mergeCell ref="D158:D162"/>
-    <mergeCell ref="E158:E162"/>
-    <mergeCell ref="F158:F162"/>
-    <mergeCell ref="G158:G162"/>
-    <mergeCell ref="H158:H162"/>
-    <mergeCell ref="I145:I149"/>
-    <mergeCell ref="J145:J149"/>
-    <mergeCell ref="C150:C154"/>
-    <mergeCell ref="D150:D154"/>
-    <mergeCell ref="E150:E154"/>
-    <mergeCell ref="F150:F154"/>
-    <mergeCell ref="G150:G154"/>
-    <mergeCell ref="H150:H154"/>
-    <mergeCell ref="I150:I154"/>
-    <mergeCell ref="J150:J154"/>
-    <mergeCell ref="C145:C149"/>
-    <mergeCell ref="D145:D149"/>
-    <mergeCell ref="E145:E149"/>
-    <mergeCell ref="F145:F149"/>
-    <mergeCell ref="G145:G149"/>
-    <mergeCell ref="H145:H149"/>
-    <mergeCell ref="I135:I139"/>
-    <mergeCell ref="J135:J139"/>
-    <mergeCell ref="C140:C144"/>
-    <mergeCell ref="D140:D144"/>
-    <mergeCell ref="E140:E144"/>
-    <mergeCell ref="F140:F144"/>
-    <mergeCell ref="G140:G144"/>
-    <mergeCell ref="H140:H144"/>
-    <mergeCell ref="I140:I144"/>
-    <mergeCell ref="J140:J144"/>
-    <mergeCell ref="C135:C139"/>
-    <mergeCell ref="D135:D139"/>
-    <mergeCell ref="E135:E139"/>
-    <mergeCell ref="F135:F139"/>
-    <mergeCell ref="G135:G139"/>
-    <mergeCell ref="H135:H139"/>
-    <mergeCell ref="I124:I128"/>
-    <mergeCell ref="J124:J128"/>
-    <mergeCell ref="C129:C133"/>
-    <mergeCell ref="D129:D133"/>
-    <mergeCell ref="E129:E133"/>
-    <mergeCell ref="F129:F133"/>
-    <mergeCell ref="G129:G133"/>
-    <mergeCell ref="H129:H133"/>
-    <mergeCell ref="I129:I133"/>
-    <mergeCell ref="J129:J133"/>
-    <mergeCell ref="C124:C128"/>
-    <mergeCell ref="D124:D128"/>
-    <mergeCell ref="E124:E128"/>
-    <mergeCell ref="F124:F128"/>
-    <mergeCell ref="G124:G128"/>
-    <mergeCell ref="H124:H128"/>
-    <mergeCell ref="I114:I118"/>
-    <mergeCell ref="J114:J118"/>
-    <mergeCell ref="C119:C123"/>
-    <mergeCell ref="D119:D123"/>
-    <mergeCell ref="E119:E123"/>
-    <mergeCell ref="F119:F123"/>
-    <mergeCell ref="G119:G123"/>
-    <mergeCell ref="H119:H123"/>
-    <mergeCell ref="I119:I123"/>
-    <mergeCell ref="J119:J123"/>
-    <mergeCell ref="C114:C118"/>
-    <mergeCell ref="D114:D118"/>
-    <mergeCell ref="E114:E118"/>
-    <mergeCell ref="F114:F118"/>
-    <mergeCell ref="G114:G118"/>
-    <mergeCell ref="H114:H118"/>
-    <mergeCell ref="I103:I107"/>
-    <mergeCell ref="J103:J107"/>
-    <mergeCell ref="C108:C112"/>
-    <mergeCell ref="D108:D112"/>
-    <mergeCell ref="E108:E112"/>
-    <mergeCell ref="F108:F112"/>
-    <mergeCell ref="G108:G112"/>
-    <mergeCell ref="H108:H112"/>
-    <mergeCell ref="I108:I112"/>
-    <mergeCell ref="J108:J112"/>
-    <mergeCell ref="C103:C107"/>
-    <mergeCell ref="D103:D107"/>
-    <mergeCell ref="E103:E107"/>
-    <mergeCell ref="F103:F107"/>
-    <mergeCell ref="G103:G107"/>
-    <mergeCell ref="H103:H107"/>
-    <mergeCell ref="I93:I97"/>
-    <mergeCell ref="J93:J97"/>
-    <mergeCell ref="C98:C102"/>
-    <mergeCell ref="D98:D102"/>
-    <mergeCell ref="E98:E102"/>
-    <mergeCell ref="F98:F102"/>
-    <mergeCell ref="G98:G102"/>
-    <mergeCell ref="H98:H102"/>
-    <mergeCell ref="I98:I102"/>
-    <mergeCell ref="J98:J102"/>
-    <mergeCell ref="C93:C97"/>
-    <mergeCell ref="D93:D97"/>
-    <mergeCell ref="E93:E97"/>
-    <mergeCell ref="F93:F97"/>
-    <mergeCell ref="G93:G97"/>
-    <mergeCell ref="H93:H97"/>
-    <mergeCell ref="I81:I85"/>
-    <mergeCell ref="J81:J85"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="D86:D90"/>
-    <mergeCell ref="E86:E90"/>
-    <mergeCell ref="F86:F90"/>
-    <mergeCell ref="G86:G90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="I86:I90"/>
-    <mergeCell ref="J86:J90"/>
-    <mergeCell ref="C81:C85"/>
-    <mergeCell ref="D81:D85"/>
-    <mergeCell ref="E81:E85"/>
-    <mergeCell ref="F81:F85"/>
-    <mergeCell ref="G81:G85"/>
-    <mergeCell ref="H81:H85"/>
-    <mergeCell ref="I71:I75"/>
-    <mergeCell ref="J71:J75"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="E76:E80"/>
-    <mergeCell ref="F76:F80"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="H76:H80"/>
-    <mergeCell ref="I76:I80"/>
-    <mergeCell ref="J76:J80"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="J60:J64"/>
-    <mergeCell ref="C65:C69"/>
-    <mergeCell ref="D65:D69"/>
-    <mergeCell ref="E65:E69"/>
-    <mergeCell ref="F65:F69"/>
-    <mergeCell ref="G65:G69"/>
-    <mergeCell ref="H65:H69"/>
-    <mergeCell ref="I65:I69"/>
-    <mergeCell ref="J65:J69"/>
-    <mergeCell ref="C60:C64"/>
-    <mergeCell ref="D60:D64"/>
-    <mergeCell ref="E60:E64"/>
-    <mergeCell ref="F60:F64"/>
-    <mergeCell ref="G60:G64"/>
-    <mergeCell ref="H60:H64"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="I55:I59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="D44:D48"/>
-    <mergeCell ref="E44:E48"/>
-    <mergeCell ref="F44:F48"/>
-    <mergeCell ref="G44:G48"/>
-    <mergeCell ref="H44:H48"/>
-    <mergeCell ref="I44:I48"/>
-    <mergeCell ref="J44:J48"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
